--- a/docs/asset-management/visual-asset-tracker.xlsx
+++ b/docs/asset-management/visual-asset-tracker.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Assets" sheetId="1" r:id="R6bd758f7424547e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Tracker" sheetId="2" r:id="R351ae12a33aa426c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="3" r:id="R8ef77026277442bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Assets" sheetId="1" r:id="R82297a63a265463c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Tracker" sheetId="2" r:id="R095941e70d2f493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="3" r:id="R46852ae541374c00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -82,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -173,6 +173,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -183,7 +185,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -193,7 +195,7 @@
         <x:color rgb="FF1F4E78"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBF7"/>
         </x:patternFill>
       </x:fill>
@@ -203,7 +205,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -213,7 +215,7 @@
         <x:color rgb="FF9D174D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE7F3"/>
         </x:patternFill>
       </x:fill>
@@ -223,7 +225,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -234,7 +236,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -244,7 +246,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -254,7 +256,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -264,7 +266,7 @@
         <x:color rgb="FF1F4E78"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBF7"/>
         </x:patternFill>
       </x:fill>
@@ -274,7 +276,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -284,7 +286,7 @@
         <x:color rgb="FF9D174D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE7F3"/>
         </x:patternFill>
       </x:fill>
@@ -294,7 +296,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -305,7 +307,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -315,7 +317,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -367,9 +369,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -569,10 +571,10 @@
       </x:c>
       <x:c r="L2" s="14"/>
       <x:c r="M2" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N2" s="14" t="str">
-        <x:v>Current v137 runtime path. Referenced by style.css.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -611,10 +613,10 @@
       </x:c>
       <x:c r="L3" s="14"/>
       <x:c r="M3" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N3" s="14" t="str">
-        <x:v>Current v137 runtime path. Referenced by app.js.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -653,10 +655,10 @@
       </x:c>
       <x:c r="L4" s="14"/>
       <x:c r="M4" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -695,10 +697,10 @@
       </x:c>
       <x:c r="L5" s="14"/>
       <x:c r="M5" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -737,10 +739,10 @@
       </x:c>
       <x:c r="L6" s="14"/>
       <x:c r="M6" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N6" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -779,10 +781,10 @@
       </x:c>
       <x:c r="L7" s="14"/>
       <x:c r="M7" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N7" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -821,10 +823,10 @@
       </x:c>
       <x:c r="L8" s="14"/>
       <x:c r="M8" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N8" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -863,10 +865,10 @@
       </x:c>
       <x:c r="L9" s="14"/>
       <x:c r="M9" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N9" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -905,10 +907,10 @@
       </x:c>
       <x:c r="L10" s="14"/>
       <x:c r="M10" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N10" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -947,10 +949,10 @@
       </x:c>
       <x:c r="L11" s="14"/>
       <x:c r="M11" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N11" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
@@ -989,10 +991,10 @@
       </x:c>
       <x:c r="L12" s="14"/>
       <x:c r="M12" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N12" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -1031,10 +1033,10 @@
       </x:c>
       <x:c r="L13" s="14"/>
       <x:c r="M13" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N13" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -1073,10 +1075,10 @@
       </x:c>
       <x:c r="L14" s="14"/>
       <x:c r="M14" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N14" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -1115,10 +1117,10 @@
       </x:c>
       <x:c r="L15" s="14"/>
       <x:c r="M15" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1150,17 +1152,17 @@
         <x:v>Landscape PNG, 16:9 recommended, 1600×900 or larger</x:v>
       </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L16" s="14"/>
       <x:c r="M16" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>Folder currently contains a README placeholder.</x:v>
+        <x:v>Artwork file is present; current app keeps this scenario locked until gameplay is rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -1192,17 +1194,17 @@
         <x:v>Landscape PNG, 16:9 recommended, 1600×900 or larger</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="K17" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L17" s="14"/>
       <x:c r="M17" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>Folder currently contains a README placeholder.</x:v>
+        <x:v>Artwork file is present; current app keeps this scenario locked until gameplay is rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
@@ -1241,10 +1243,10 @@
       </x:c>
       <x:c r="L18" s="14"/>
       <x:c r="M18" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
@@ -1283,10 +1285,10 @@
       </x:c>
       <x:c r="L19" s="14"/>
       <x:c r="M19" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>Use as drawing reference. Not a production portrait.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
@@ -1325,10 +1327,10 @@
       </x:c>
       <x:c r="L20" s="14"/>
       <x:c r="M20" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
@@ -1360,17 +1362,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K21" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L21" s="14"/>
       <x:c r="M21" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
@@ -1402,17 +1404,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L22" s="14"/>
       <x:c r="M22" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
@@ -1444,17 +1446,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L23" s="14"/>
       <x:c r="M23" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
@@ -1486,17 +1488,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L24" s="14"/>
       <x:c r="M24" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
@@ -1528,17 +1530,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Not Required</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>High</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="L25" s="14"/>
       <x:c r="M25" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Historical planned expression; not present in the current S2 asset registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
@@ -1570,17 +1572,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L26" s="14"/>
       <x:c r="M26" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
@@ -1619,10 +1621,10 @@
       </x:c>
       <x:c r="L27" s="14"/>
       <x:c r="M27" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>He/him. Older veteran returning to school in a CTE program. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
@@ -1661,7 +1663,7 @@
       </x:c>
       <x:c r="L28" s="14"/>
       <x:c r="M28" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -1703,7 +1705,7 @@
       </x:c>
       <x:c r="L29" s="14"/>
       <x:c r="M29" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -1745,7 +1747,7 @@
       </x:c>
       <x:c r="L30" s="14"/>
       <x:c r="M30" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -1787,7 +1789,7 @@
       </x:c>
       <x:c r="L31" s="14"/>
       <x:c r="M31" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -1829,7 +1831,7 @@
       </x:c>
       <x:c r="L32" s="14"/>
       <x:c r="M32" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -1871,7 +1873,7 @@
       </x:c>
       <x:c r="L33" s="14"/>
       <x:c r="M33" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -1913,10 +1915,10 @@
       </x:c>
       <x:c r="L34" s="14"/>
       <x:c r="M34" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>She/her. Rural adult learner balancing several responsibilities. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
@@ -1955,7 +1957,7 @@
       </x:c>
       <x:c r="L35" s="14"/>
       <x:c r="M35" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N35" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -1997,7 +1999,7 @@
       </x:c>
       <x:c r="L36" s="14"/>
       <x:c r="M36" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N36" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2039,7 +2041,7 @@
       </x:c>
       <x:c r="L37" s="14"/>
       <x:c r="M37" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N37" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2081,7 +2083,7 @@
       </x:c>
       <x:c r="L38" s="14"/>
       <x:c r="M38" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N38" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2123,7 +2125,7 @@
       </x:c>
       <x:c r="L39" s="14"/>
       <x:c r="M39" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N39" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2165,7 +2167,7 @@
       </x:c>
       <x:c r="L40" s="14"/>
       <x:c r="M40" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N40" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2207,10 +2209,10 @@
       </x:c>
       <x:c r="L41" s="14"/>
       <x:c r="M41" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N41" s="14" t="str">
-        <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
@@ -2249,7 +2251,7 @@
       </x:c>
       <x:c r="L42" s="14"/>
       <x:c r="M42" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N42" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2291,7 +2293,7 @@
       </x:c>
       <x:c r="L43" s="14"/>
       <x:c r="M43" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N43" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2333,7 +2335,7 @@
       </x:c>
       <x:c r="L44" s="14"/>
       <x:c r="M44" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N44" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2375,7 +2377,7 @@
       </x:c>
       <x:c r="L45" s="14"/>
       <x:c r="M45" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N45" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2417,7 +2419,7 @@
       </x:c>
       <x:c r="L46" s="14"/>
       <x:c r="M46" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N46" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2459,7 +2461,7 @@
       </x:c>
       <x:c r="L47" s="14"/>
       <x:c r="M47" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N47" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2501,10 +2503,10 @@
       </x:c>
       <x:c r="L48" s="14"/>
       <x:c r="M48" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N48" s="14" t="str">
-        <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -2543,7 +2545,7 @@
       </x:c>
       <x:c r="L49" s="14"/>
       <x:c r="M49" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N49" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2585,7 +2587,7 @@
       </x:c>
       <x:c r="L50" s="14"/>
       <x:c r="M50" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N50" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2627,7 +2629,7 @@
       </x:c>
       <x:c r="L51" s="14"/>
       <x:c r="M51" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N51" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2669,7 +2671,7 @@
       </x:c>
       <x:c r="L52" s="14"/>
       <x:c r="M52" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N52" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2711,7 +2713,7 @@
       </x:c>
       <x:c r="L53" s="14"/>
       <x:c r="M53" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N53" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2753,7 +2755,7 @@
       </x:c>
       <x:c r="L54" s="14"/>
       <x:c r="M54" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N54" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2795,10 +2797,10 @@
       </x:c>
       <x:c r="L55" s="14"/>
       <x:c r="M55" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N55" s="14" t="str">
-        <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="34" customHeight="1">
@@ -2837,7 +2839,7 @@
       </x:c>
       <x:c r="L56" s="14"/>
       <x:c r="M56" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N56" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -2879,7 +2881,7 @@
       </x:c>
       <x:c r="L57" s="14"/>
       <x:c r="M57" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N57" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -2921,7 +2923,7 @@
       </x:c>
       <x:c r="L58" s="14"/>
       <x:c r="M58" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N58" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -2963,7 +2965,7 @@
       </x:c>
       <x:c r="L59" s="14"/>
       <x:c r="M59" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N59" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3005,7 +3007,7 @@
       </x:c>
       <x:c r="L60" s="14"/>
       <x:c r="M60" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N60" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3047,7 +3049,7 @@
       </x:c>
       <x:c r="L61" s="14"/>
       <x:c r="M61" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N61" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3055,170 +3057,380 @@
     </x:row>
     <x:row r="62" ht="34" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
-        <x:v>Branding</x:v>
+        <x:v>Background</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>promptcraft-logo.png</x:v>
+        <x:v>s1-science-wing.jpg</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>assets/images/branding/</x:v>
+        <x:v>assets/images/backgrounds/gfc/</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>assets/images/branding/promptcraft-logo.png</x:v>
+        <x:v>assets/images/backgrounds/gfc/s1-science-wing.jpg</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>Menu, splash, and documentation</x:v>
+        <x:v>S1: Engagement VN/workstation</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>GFC campus background</x:v>
       </x:c>
       <x:c r="H62" s="14" t="str">
-        <x:v>PromptCraft logo or wordmark.</x:v>
+        <x:v>Great Falls College Science Wing environment used by S1.</x:v>
       </x:c>
       <x:c r="I62" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>Landscape JPG, high-resolution</x:v>
       </x:c>
       <x:c r="J62" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K62" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="L62" s="14"/>
       <x:c r="M62" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N62" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 scenario background registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="34" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
-        <x:v>Branding</x:v>
+        <x:v>Background</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>shanel-headshot.png</x:v>
+        <x:v>s2-study-lounge.jpg</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>assets/images/branding/</x:v>
+        <x:v>assets/images/backgrounds/gfc/</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>assets/images/branding/shanel-headshot.png</x:v>
+        <x:v>assets/images/backgrounds/gfc/s2-study-lounge.jpg</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>About PromptCraft panel</x:v>
+        <x:v>S2: Metacognition VN/workstation</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>GFC campus background</x:v>
       </x:c>
       <x:c r="H63" s="14" t="str">
-        <x:v>Optional professional headshot.</x:v>
+        <x:v>Great Falls College Study Lounge environment used by S2.</x:v>
       </x:c>
       <x:c r="I63" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>Landscape JPG, high-resolution</x:v>
       </x:c>
       <x:c r="J63" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K63" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="L63" s="14"/>
       <x:c r="M63" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N63" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 scenario background registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="34" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>Institutional</x:v>
+        <x:v>UI / Babbage</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>gfcmsu-wordmark.png</x:v>
+        <x:v>babbage-mark.svg</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>assets/images/institutional/</x:v>
+        <x:v>assets/images/ui/</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>assets/images/institutional/gfcmsu-wordmark.png</x:v>
+        <x:v>assets/images/ui/babbage-mark.svg</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>Institutional context panel</x:v>
+        <x:v>PromptCraft brand menus and Babbage identity</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>SVG mark</x:v>
       </x:c>
       <x:c r="H64" s="14" t="str">
-        <x:v>Optional Great Falls College MSU wordmark.</x:v>
+        <x:v>Compact Babbage portrait/mark used in PromptCraft branding and interface chrome.</x:v>
       </x:c>
       <x:c r="I64" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>SVG, transparent</x:v>
       </x:c>
       <x:c r="J64" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K64" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="L64" s="14"/>
       <x:c r="M64" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N64" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="34" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>Institutional</x:v>
+        <x:v>UI / Babbage</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>msu-eds-wordmark.png</x:v>
+        <x:v>charles-babbage.png</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>assets/images/institutional/</x:v>
+        <x:v>assets/images/ui/</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>assets/images/institutional/msu-eds-wordmark.png</x:v>
+        <x:v>assets/images/ui/charles-babbage.png</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>Academic context panel</x:v>
+        <x:v>Meet Babbage page</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>Portrait image</x:v>
       </x:c>
       <x:c r="H65" s="14" t="str">
-        <x:v>Optional Montana State University Ed.S. mark.</x:v>
+        <x:v>Charles Babbage portrait used on the Meet Babbage information page.</x:v>
       </x:c>
       <x:c r="I65" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>PNG</x:v>
       </x:c>
       <x:c r="J65" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K65" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="L65" s="14"/>
       <x:c r="M65" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N65" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Background</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>desk-extension.png</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>assets/images/backgrounds/</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>assets/images/backgrounds/desk-extension.png</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>Shared workstation composition</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>Background extension</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>Desk/workstation extension used by shared Babbage layouts.</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>PNG</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L66"/>
+      <x:c r="M66" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N66" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>Brand / Print</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>great-falls-college-logo.jpg</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>assets/images/brand/</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>assets/images/brand/great-falls-college-logo.jpg</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>Printable Babbage report</x:v>
+      </x:c>
+      <x:c r="G67" t="str">
+        <x:v>Institutional logo</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>Great Falls College logo used in the document-first printable diagnosis report.</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>JPG</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L67"/>
+      <x:c r="M67" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N67" t="str">
+        <x:v>Current V429 runtime image; print/report use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>UI / Babbage</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>babbage-engine.webp</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>assets/images/ui/</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>assets/images/ui/babbage-engine.webp</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>Teaching Progress panel</x:v>
+      </x:c>
+      <x:c r="G68" t="str">
+        <x:v>Historical machine image</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>Historic Babbage engine image used in the expanded teaching-progression panel.</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>WEBP</x:v>
+      </x:c>
+      <x:c r="J68" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L68"/>
+      <x:c r="M68" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N68" t="str">
+        <x:v>Current V429 runtime image; Teaching Progress.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>Reference</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>UI / Babbage</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>babbage-engine-plate.svg</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>assets/images/ui/</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>assets/images/ui/babbage-engine-plate.svg</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>Development reference</x:v>
+      </x:c>
+      <x:c r="G69" t="str">
+        <x:v>Legacy/reference plate</x:v>
+      </x:c>
+      <x:c r="H69" t="str">
+        <x:v>Earlier Babbage engine plate retained only as a development reference.</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>SVG</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>Reference Only</x:v>
+      </x:c>
+      <x:c r="K69" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="L69"/>
+      <x:c r="M69" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N69" t="str">
+        <x:v>Not loaded by the current application.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>UI / Utility</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>promptcraft-qr.png</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>assets/ui/</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>assets/ui/promptcraft-qr.png</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>Main menu / Prompt Lab launch</x:v>
+      </x:c>
+      <x:c r="G70" t="str">
+        <x:v>QR code</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>PromptCraft QR code shown in the Prompt Lab landing experience.</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>PNG</x:v>
+      </x:c>
+      <x:c r="J70" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L70"/>
+      <x:c r="M70" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N70" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3342,13 +3554,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J2" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K2" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L2" s="14" t="str">
-        <x:v>Current v137 runtime path. Referenced by style.css.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -3378,13 +3590,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J3" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K3" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L3" s="14" t="str">
-        <x:v>Current v137 runtime path. Referenced by app.js.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -3414,13 +3626,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J4" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K4" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -3450,13 +3662,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J5" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K5" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L5" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -3486,13 +3698,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J6" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K6" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L6" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -3522,13 +3734,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J7" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K7" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L7" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -3558,13 +3770,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K8" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L8" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -3594,13 +3806,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K9" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L9" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -3630,13 +3842,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K10" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L10" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -3666,13 +3878,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K11" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L11" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
@@ -3702,13 +3914,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K12" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L12" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -3738,13 +3950,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K13" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L13" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -3774,13 +3986,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K14" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L14" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -3810,13 +4022,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K15" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L15" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -3830,10 +4042,10 @@
         <x:v>assets/images/scenes/scenario-07-overreliance/scene.png</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F16" s="14"/>
       <x:c r="G16" s="14" t="str">
@@ -3842,15 +4054,17 @@
       <x:c r="H16" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I16" s="18"/>
+      <x:c r="I16" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L16" s="14" t="str">
-        <x:v>Folder currently contains a README placeholder.</x:v>
+        <x:v>Artwork file is present; current app keeps this scenario locked until gameplay is rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -3864,10 +4078,10 @@
         <x:v>assets/images/scenes/scenario-08-reflect-revise/scene.png</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F17" s="14"/>
       <x:c r="G17" s="14" t="str">
@@ -3876,15 +4090,17 @@
       <x:c r="H17" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I17" s="18"/>
+      <x:c r="I17" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K17" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="L17" s="14" t="str">
-        <x:v>Folder currently contains a README placeholder.</x:v>
+        <x:v>Artwork file is present; current app keeps this scenario locked until gameplay is rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
@@ -3914,13 +4130,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K18" s="14" t="str">
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="L18" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
@@ -3950,13 +4166,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K19" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>Use as drawing reference. Not a production portrait.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
@@ -3986,13 +4202,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K20" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
@@ -4006,10 +4222,10 @@
         <x:v>assets/images/characters/students/jordan/neutral.png</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F21" s="14"/>
       <x:c r="G21" s="14" t="str">
@@ -4018,15 +4234,17 @@
       <x:c r="H21" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I21" s="18"/>
+      <x:c r="I21" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K21" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
@@ -4040,10 +4258,10 @@
         <x:v>assets/images/characters/students/jordan/uncertain.png</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F22" s="14"/>
       <x:c r="G22" s="14" t="str">
@@ -4052,15 +4270,17 @@
       <x:c r="H22" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I22" s="18"/>
+      <x:c r="I22" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
@@ -4074,10 +4294,10 @@
         <x:v>assets/images/characters/students/jordan/frustrated.png</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F23" s="14"/>
       <x:c r="G23" s="14" t="str">
@@ -4086,15 +4306,17 @@
       <x:c r="H23" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I23" s="18"/>
+      <x:c r="I23" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
@@ -4108,10 +4330,10 @@
         <x:v>assets/images/characters/students/jordan/thinking.png</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F24" s="14"/>
       <x:c r="G24" s="14" t="str">
@@ -4120,15 +4342,17 @@
       <x:c r="H24" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I24" s="18"/>
+      <x:c r="I24" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
@@ -4149,20 +4373,22 @@
       </x:c>
       <x:c r="F25" s="14"/>
       <x:c r="G25" s="14" t="str">
-        <x:v>High</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I25" s="18"/>
+      <x:c r="I25" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Not Required</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Historical planned expression; not present in the current S2 asset registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
@@ -4176,10 +4402,10 @@
         <x:v>assets/images/characters/students/jordan/confident.png</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F26" s="14"/>
       <x:c r="G26" s="14" t="str">
@@ -4188,15 +4414,17 @@
       <x:c r="H26" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I26" s="18"/>
+      <x:c r="I26" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
@@ -4226,13 +4454,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K27" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>He/him. Older veteran returning to school in a CTE program. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
@@ -4258,9 +4486,11 @@
       <x:c r="H28" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I28" s="18"/>
+      <x:c r="I28" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K28" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4292,9 +4522,11 @@
       <x:c r="H29" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I29" s="18"/>
+      <x:c r="I29" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K29" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4326,9 +4558,11 @@
       <x:c r="H30" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I30" s="18"/>
+      <x:c r="I30" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K30" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4360,9 +4594,11 @@
       <x:c r="H31" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I31" s="18"/>
+      <x:c r="I31" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K31" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4394,9 +4630,11 @@
       <x:c r="H32" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I32" s="18"/>
+      <x:c r="I32" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K32" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4428,9 +4666,11 @@
       <x:c r="H33" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I33" s="18"/>
+      <x:c r="I33" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K33" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4466,13 +4706,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K34" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
-        <x:v>She/her. Rural adult learner balancing several responsibilities. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
@@ -4498,9 +4738,11 @@
       <x:c r="H35" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I35" s="18"/>
+      <x:c r="I35" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K35" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4532,9 +4774,11 @@
       <x:c r="H36" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I36" s="18"/>
+      <x:c r="I36" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K36" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4566,9 +4810,11 @@
       <x:c r="H37" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I37" s="18"/>
+      <x:c r="I37" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K37" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4600,9 +4846,11 @@
       <x:c r="H38" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I38" s="18"/>
+      <x:c r="I38" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K38" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4634,9 +4882,11 @@
       <x:c r="H39" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I39" s="18"/>
+      <x:c r="I39" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K39" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4668,9 +4918,11 @@
       <x:c r="H40" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I40" s="18"/>
+      <x:c r="I40" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K40" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4706,13 +4958,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K41" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L41" s="14" t="str">
-        <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
@@ -4738,9 +4990,11 @@
       <x:c r="H42" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I42" s="18"/>
+      <x:c r="I42" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K42" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4772,9 +5026,11 @@
       <x:c r="H43" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I43" s="18"/>
+      <x:c r="I43" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K43" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4806,9 +5062,11 @@
       <x:c r="H44" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I44" s="18"/>
+      <x:c r="I44" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K44" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4840,9 +5098,11 @@
       <x:c r="H45" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I45" s="18"/>
+      <x:c r="I45" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K45" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4874,9 +5134,11 @@
       <x:c r="H46" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I46" s="18"/>
+      <x:c r="I46" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K46" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4908,9 +5170,11 @@
       <x:c r="H47" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I47" s="18"/>
+      <x:c r="I47" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K47" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -4946,13 +5210,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K48" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L48" s="14" t="str">
-        <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -4978,9 +5242,11 @@
       <x:c r="H49" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I49" s="18"/>
+      <x:c r="I49" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K49" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5012,9 +5278,11 @@
       <x:c r="H50" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I50" s="18"/>
+      <x:c r="I50" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J50" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K50" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5046,9 +5314,11 @@
       <x:c r="H51" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I51" s="18"/>
+      <x:c r="I51" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J51" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K51" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5080,9 +5350,11 @@
       <x:c r="H52" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I52" s="18"/>
+      <x:c r="I52" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J52" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K52" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5114,9 +5386,11 @@
       <x:c r="H53" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I53" s="18"/>
+      <x:c r="I53" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J53" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K53" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5148,9 +5422,11 @@
       <x:c r="H54" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I54" s="18"/>
+      <x:c r="I54" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J54" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K54" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5186,13 +5462,13 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="J55" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K55" s="14" t="str">
         <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="L55" s="14" t="str">
-        <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="34" customHeight="1">
@@ -5218,9 +5494,11 @@
       <x:c r="H56" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I56" s="18"/>
+      <x:c r="I56" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J56" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K56" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5252,9 +5530,11 @@
       <x:c r="H57" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I57" s="18"/>
+      <x:c r="I57" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J57" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K57" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5286,9 +5566,11 @@
       <x:c r="H58" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I58" s="18"/>
+      <x:c r="I58" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J58" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K58" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5320,9 +5602,11 @@
       <x:c r="H59" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I59" s="18"/>
+      <x:c r="I59" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J59" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K59" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5354,9 +5638,11 @@
       <x:c r="H60" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I60" s="18"/>
+      <x:c r="I60" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J60" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K60" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5388,9 +5674,11 @@
       <x:c r="H61" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I61" s="18"/>
+      <x:c r="I61" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J61" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K61" s="14" t="str">
         <x:v>Not Started</x:v>
@@ -5401,138 +5689,326 @@
     </x:row>
     <x:row r="62" ht="34" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>promptcraft-logo.png</x:v>
+        <x:v>s1-science-wing.jpg</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
-        <x:v>assets/images/branding/</x:v>
+        <x:v>assets/images/backgrounds/gfc/</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>assets/images/branding/promptcraft-logo.png</x:v>
+        <x:v>assets/images/backgrounds/gfc/s1-science-wing.jpg</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F62" s="14"/>
       <x:c r="G62" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H62" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I62" s="18"/>
+      <x:c r="I62" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J62" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K62" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L62" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 scenario background registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="34" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>shanel-headshot.png</x:v>
+        <x:v>s2-study-lounge.jpg</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
-        <x:v>assets/images/branding/</x:v>
+        <x:v>assets/images/backgrounds/gfc/</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>assets/images/branding/shanel-headshot.png</x:v>
+        <x:v>assets/images/backgrounds/gfc/s2-study-lounge.jpg</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F63" s="14"/>
       <x:c r="G63" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H63" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I63" s="18"/>
+      <x:c r="I63" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J63" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K63" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L63" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 scenario background registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="34" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>gfcmsu-wordmark.png</x:v>
+        <x:v>babbage-mark.svg</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>assets/images/institutional/</x:v>
+        <x:v>assets/images/ui/</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>assets/images/institutional/gfcmsu-wordmark.png</x:v>
+        <x:v>assets/images/ui/babbage-mark.svg</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F64" s="14"/>
       <x:c r="G64" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H64" s="14" t="str">
         <x:v>Shanel</x:v>
       </x:c>
-      <x:c r="I64" s="18"/>
+      <x:c r="I64" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
       <x:c r="J64" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="K64" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="L64" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="34" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>msu-eds-wordmark.png</x:v>
+        <x:v>charles-babbage.png</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>assets/images/institutional/</x:v>
+        <x:v>assets/images/ui/</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>assets/images/institutional/msu-eds-wordmark.png</x:v>
+        <x:v>assets/images/ui/charles-babbage.png</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F65" s="14"/>
       <x:c r="G65" s="14" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H65" s="14" t="str">
+        <x:v>Shanel</x:v>
+      </x:c>
+      <x:c r="I65" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="J65" s="18" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="K65" s="14" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="L65" s="14" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>desk-extension.png</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>assets/images/backgrounds/</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>assets/images/backgrounds/desk-extension.png</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F66"/>
+      <x:c r="G66" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>Shanel</x:v>
+      </x:c>
+      <x:c r="I66" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="J66" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="L66" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>great-falls-college-logo.jpg</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>assets/images/brand/</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>assets/images/brand/great-falls-college-logo.jpg</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F67"/>
+      <x:c r="G67" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>Shanel</x:v>
+      </x:c>
+      <x:c r="I67" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="J67" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="L67" t="str">
+        <x:v>Current V429 runtime image; print/report use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>babbage-engine.webp</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>assets/images/ui/</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>assets/images/ui/babbage-engine.webp</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F68"/>
+      <x:c r="G68" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>Shanel</x:v>
+      </x:c>
+      <x:c r="I68" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="J68" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="L68" t="str">
+        <x:v>Current V429 runtime image; Teaching Progress.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>babbage-engine-plate.svg</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>assets/images/ui/</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>assets/images/ui/babbage-engine-plate.svg</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F69"/>
+      <x:c r="G69" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="H65" s="14" t="str">
-        <x:v>Shanel</x:v>
-      </x:c>
-      <x:c r="I65" s="18"/>
-      <x:c r="J65" s="18" t="n">
-        <x:v>46226</x:v>
-      </x:c>
-      <x:c r="K65" s="14" t="str">
-        <x:v>Not Started</x:v>
-      </x:c>
-      <x:c r="L65" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+      <x:c r="H69" t="str">
+        <x:v>Shanel</x:v>
+      </x:c>
+      <x:c r="I69" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="J69" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="K69" t="str">
+        <x:v>Reference Only</x:v>
+      </x:c>
+      <x:c r="L69" t="str">
+        <x:v>Not loaded by the current application.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>promptcraft-qr.png</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>assets/ui/</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>assets/ui/promptcraft-qr.png</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F70"/>
+      <x:c r="G70" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>Shanel</x:v>
+      </x:c>
+      <x:c r="I70" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="J70" s="43" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="L70" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5592,16 +6068,20 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="23" t="str">
-        <x:v>PromptCraft Visual Asset Tracker — v137</x:v>
+        <x:v>PromptCraft Visual Asset Tracker — V429 / asset manifest v144</x:v>
       </x:c>
       <x:c r="B1" s="23"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="31" t="str">
         <x:v>Workbook purpose</x:v>
       </x:c>
       <x:c r="B3" s="38" t="str">
-        <x:v>Production tracker for current, reference, and planned PromptCraft image assets.</x:v>
+        <x:v>Detailed production tracker for PromptCraft backgrounds, scenario art, characters, Babbage/brand UI assets, and development references.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5609,7 +6089,7 @@
         <x:v>Code baseline</x:v>
       </x:c>
       <x:c r="B4" s="38" t="str">
-        <x:v>PromptCraft v137 organized asset structure.</x:v>
+        <x:v>PROMPTCRAFT_V429; current documentation/cache revision 446.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5617,7 +6097,7 @@
         <x:v>Visual source of truth</x:v>
       </x:c>
       <x:c r="B5" s="38" t="str">
-        <x:v>Current paths in index.html, style.css, functions/app.js, and assets/asset-manifest.json.</x:v>
+        <x:v>assets/asset-manifest.json (v144), src/js/app/config-and-assets.js, and current asset files under assets/.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5625,7 +6105,7 @@
         <x:v>Path convention</x:v>
       </x:c>
       <x:c r="B6" s="38" t="str">
-        <x:v>All production images now live under assets/images/. Folder and Full path columns use the current v137 structure.</x:v>
+        <x:v>Production images live under assets/images/ except utility files intentionally under assets/ui/. Use Full path as the canonical repository path.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5633,23 +6113,23 @@
         <x:v>Student portraits</x:v>
       </x:c>
       <x:c r="B7" s="38" t="str">
-        <x:v>Reference sheets are stored under each student's references/ folder. Final transparent portraits belong directly in that student's folder.</x:v>
+        <x:v>Jordan production portraits are active in S2. Other student character folders remain planned/reference material until their scenarios are rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="31" t="str">
-        <x:v>S2 priority</x:v>
+        <x:v>Scenario art</x:v>
       </x:c>
       <x:c r="B8" s="38" t="str">
-        <x:v>Jordan's six planned portraits are marked High priority because Scenario 2 is the current development focus.</x:v>
+        <x:v>S1-S6 and completion art are classified as runtime images; S7-S8 scene files are present but remain planned while those scenarios are locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="31" t="str">
-        <x:v>Audio</x:v>
+        <x:v>Babbage / brand</x:v>
       </x:c>
       <x:c r="B9" s="38" t="str">
-        <x:v>Audio is tracked in the PromptCraft Master Asset Tracker v137 rather than duplicated here.</x:v>
+        <x:v>Includes the Babbage mark, Charles Babbage portrait, Babbage engine, print logo, QR code, and retained reference plate.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5657,7 +6137,7 @@
         <x:v>Workflow</x:v>
       </x:c>
       <x:c r="B10" s="38" t="str">
-        <x:v>Update Production status, Needs revision?, and Last updated as each asset is drawn, replaced, and tested.</x:v>
+        <x:v>Update Production status, Needs revision?, and Last updated as assets are replaced and tested. If this workbook conflicts with asset-manifest.json, update the workbook.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
